--- a/www/download/IND.gdp.s.mv.rpA1.xlsx
+++ b/www/download/IND.gdp.s.mv.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7600.512</t>
+          <t>7600511700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7613.761</t>
+          <t>7613761200</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7690.54</t>
+          <t>7690540000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7765.948</t>
+          <t>7765947800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7902.833</t>
+          <t>7902832600</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8013.502</t>
+          <t>8013502200</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8006.477</t>
+          <t>8006477300</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8078.917</t>
+          <t>8078917200</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8240.178</t>
+          <t>8240178120</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8339.207</t>
+          <t>8339207400</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8582.071</t>
+          <t>8582071244.64583</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8843.494</t>
+          <t>8843493922.99553</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>9083.497</t>
+          <t>9083497170.11503</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9812.963</t>
+          <t>9812963347.5531</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10323.609</t>
+          <t>10323608974.885</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3467.213</t>
+          <t>3467213000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3455.681</t>
+          <t>3455681000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3473.68</t>
+          <t>3473680000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3472.368</t>
+          <t>3472368000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3452.871</t>
+          <t>3452871000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3466.033</t>
+          <t>3466033000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3464.642</t>
+          <t>3464642000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3426.702</t>
+          <t>3426702000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3437.044</t>
+          <t>3437044000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3445.78</t>
+          <t>3445780000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3391.947</t>
+          <t>3391947000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3386.029</t>
+          <t>3386029000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3403.833</t>
+          <t>3403833000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3475.505</t>
+          <t>3475504566.99832</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3244.006</t>
+          <t>3244005709.59928</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2644.885</t>
+          <t>2644884976.88788</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2611.457</t>
+          <t>2611456538.74614</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2622.384</t>
+          <t>2622383522.29246</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2640.058</t>
+          <t>2640057926.02361</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2665.412</t>
+          <t>2665411630.59851</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2723.422</t>
+          <t>2723422052.15245</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2734.402</t>
+          <t>2734401947.43295</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2682.234</t>
+          <t>2682234091.96582</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2664.038</t>
+          <t>2664037662.86156</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2663.951</t>
+          <t>2663950545.87004</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2638.288</t>
+          <t>2638288062.32277</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2665.495</t>
+          <t>2665494682.89325</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2695.838</t>
+          <t>2695837875.11875</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2711.455</t>
+          <t>2711455230.61422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2653.904</t>
+          <t>2653904109.09152</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4046.527</t>
+          <t>4046527144.99397</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4103.145</t>
+          <t>4103144656.09807</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3974.814</t>
+          <t>3974814384.40038</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3806.137</t>
+          <t>3806136517.14592</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3595.999</t>
+          <t>3595999123.3511</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3452.947</t>
+          <t>3452947352.11324</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3325.187</t>
+          <t>3325186964.26779</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3321.965</t>
+          <t>3321964578.06737</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3331.628</t>
+          <t>3331627831.29498</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3421.133</t>
+          <t>3421132813.22682</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3489.347</t>
+          <t>3489347351.61952</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3599.066</t>
+          <t>3599065702.20611</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3679.72</t>
+          <t>3679720139.52698</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3627.101</t>
+          <t>3627100553.10887</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3533.766</t>
+          <t>3533765814.26293</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>86211.3</t>
+          <t>86211299706.4018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>83875.219</t>
+          <t>83875218585.1343</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84873.732</t>
+          <t>84873732457.1371</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>83325.51</t>
+          <t>83325509931.2943</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>86687.925</t>
+          <t>86687924832.88</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>87257.862</t>
+          <t>87257861560.179</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>86351.459</t>
+          <t>86351459132.1141</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>88891.224</t>
+          <t>88891223732.5434</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>89863.245</t>
+          <t>89863245247.544</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>94670.259</t>
+          <t>94670259124.4999</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>96104.88</t>
+          <t>96104880362.2399</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>95960.44</t>
+          <t>95960440142.8321</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>97455.978</t>
+          <t>97455977565.8679</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100077.188</t>
+          <t>100077188112.293</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>98458.434</t>
+          <t>98458434353.412</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11046.668</t>
+          <t>11046667953.8974</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11180.27</t>
+          <t>11180270435.5511</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11366.321</t>
+          <t>11366320537.7864</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11416.943</t>
+          <t>11416943343.5617</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11577.091</t>
+          <t>11577090588.8751</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11783.121</t>
+          <t>11783121082.8557</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11634.89</t>
+          <t>11634889935.7461</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11695.729</t>
+          <t>11695729319.0936</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11792.766</t>
+          <t>11792766114.5529</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12108.107</t>
+          <t>12108106728.9406</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12163.9</t>
+          <t>12163899664.5301</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12287.489</t>
+          <t>12287488573.6924</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12470.271</t>
+          <t>12470270723.1141</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12503.118</t>
+          <t>12503118170.9134</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12197.981</t>
+          <t>12197981135.2108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>927359.119</t>
+          <t>927359118910.789</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>929929.814</t>
+          <t>929929813619.566</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>933533.435</t>
+          <t>933533434522.381</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>930370.776</t>
+          <t>930370776087.752</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>937817.747</t>
+          <t>937817747349.174</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>948107.806</t>
+          <t>948107806214.009</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>966369.722</t>
+          <t>966369722461.129</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>989092.749</t>
+          <t>989092749439.088</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1006639.806</t>
+          <t>1006639805625.82</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1020110.349</t>
+          <t>1020110349379.16</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1023503.052</t>
+          <t>1023503051701.24</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1054484.694</t>
+          <t>1054484694103.47</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1076703.09</t>
+          <t>1076703089611.7</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1107483.703</t>
+          <t>1107483703160.28</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1110293.654</t>
+          <t>1110293653915.7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>263.441</t>
+          <t>263441246.359666</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>259.855</t>
+          <t>259854833.536317</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>258.156</t>
+          <t>258155719.163838</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>257.788</t>
+          <t>257787648.463305</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>258.328</t>
+          <t>258328143.739714</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>258.916</t>
+          <t>258916000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>260.436</t>
+          <t>260436000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>260.331</t>
+          <t>260331000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>269.335</t>
+          <t>269335000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>273.832</t>
+          <t>273832000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>275.243</t>
+          <t>275243000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>278.466</t>
+          <t>278466000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>283.387</t>
+          <t>283387000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>278.575</t>
+          <t>278574974.798666</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>282.012</t>
+          <t>282012076.845781</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6402.617</t>
+          <t>6402617000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6485.192</t>
+          <t>6485192000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6446.657</t>
+          <t>6446657000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6325.73</t>
+          <t>6325730000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6085.864</t>
+          <t>6085864000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5991.293</t>
+          <t>5991293000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5756.066</t>
+          <t>5756066000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5659.98</t>
+          <t>5659980000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5538.096</t>
+          <t>5538096000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5558.336</t>
+          <t>5558336000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5618.71</t>
+          <t>5618710000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5689.107</t>
+          <t>5689107000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5779.303</t>
+          <t>5779303000</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5903.721</t>
+          <t>5903721098.81198</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5565.062</t>
+          <t>5565061504.42354</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30544.614</t>
+          <t>30544613977.9518</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29561.813</t>
+          <t>29561813394.1238</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29130.824</t>
+          <t>29130823720.2806</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29180.243</t>
+          <t>29180242583.1754</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28904.383</t>
+          <t>28904383491.8446</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28702.257</t>
+          <t>28702256708.3024</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28206.608</t>
+          <t>28206607677.6067</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27607.394</t>
+          <t>27607393826.0056</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27103.027</t>
+          <t>27103026912.1813</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27178.128</t>
+          <t>27178127830.1887</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>26805.241</t>
+          <t>26805241151.4865</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>26764.734</t>
+          <t>26764733829.6882</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>27092.35</t>
+          <t>27092350295.3203</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>27046.949</t>
+          <t>27046949132.8123</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>26146.709</t>
+          <t>26146708723.6509</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2232.081</t>
+          <t>2232081000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2214.223</t>
+          <t>2214223000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2254.895</t>
+          <t>2254895000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2304.053</t>
+          <t>2304053000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2318.406</t>
+          <t>2318406000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2340.219</t>
+          <t>2340219000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2346.797</t>
+          <t>2346797000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2327.81</t>
+          <t>2327810000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2281.399</t>
+          <t>2281399000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2248.595</t>
+          <t>2248595000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2255.948</t>
+          <t>2255948000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2300.909</t>
+          <t>2300909000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2314.612</t>
+          <t>2314612000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2326.031</t>
+          <t>2326030735.34952</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2289.028</t>
+          <t>2289027968.72536</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12057.839</t>
+          <t>12057839276.7014</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12132.699</t>
+          <t>12132698704.2174</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12571.819</t>
+          <t>12571819369.6346</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13092.628</t>
+          <t>13092627729.1083</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13678.386</t>
+          <t>13678386296.9535</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14328.961</t>
+          <t>14328961200</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14698.135</t>
+          <t>14698135100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15014.151</t>
+          <t>15014150700</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15264.345</t>
+          <t>15264345100</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>15511.477</t>
+          <t>15511477100</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>15853.559</t>
+          <t>15853559300</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16235.579</t>
+          <t>16235578800</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>16403.077</t>
+          <t>16403077400</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>15718.863</t>
+          <t>15718862570.5005</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>14017.103</t>
+          <t>14017102929.8905</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>782.102</t>
+          <t>782101882.575398</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>753.133</t>
+          <t>753133465.081181</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>740.619</t>
+          <t>740618963.206468</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>715.843</t>
+          <t>715843237.034939</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>666.322</t>
+          <t>666321602.174527</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>644.288</t>
+          <t>644288038.902677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>654.892</t>
+          <t>654892049.058957</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>650.317</t>
+          <t>650316806.699255</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>680.698</t>
+          <t>680698141.005312</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>701.44</t>
+          <t>701440081.865048</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>696.057</t>
+          <t>696057363.171713</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>738.433</t>
+          <t>738433067.071925</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>751.381</t>
+          <t>751381285.466012</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>736.419</t>
+          <t>736418564.598609</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>610.325</t>
+          <t>610324795.603824</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2206.7</t>
+          <t>2206700000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2212.3</t>
+          <t>2212300000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2275.8</t>
+          <t>2275800000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2297.2</t>
+          <t>2297200000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2345.1</t>
+          <t>2345100000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2354.1</t>
+          <t>2354100000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2341.4</t>
+          <t>2341400000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2334.9</t>
+          <t>2334900000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2305.4</t>
+          <t>2305400000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2308.6</t>
+          <t>2308600000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2318.4</t>
+          <t>2318400000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2352.5</t>
+          <t>2352500000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2388.6</t>
+          <t>2388600000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2415.662</t>
+          <t>2415662342.89855</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2282.511</t>
+          <t>2282510706.58301</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17610.004</t>
+          <t>17610003955.0838</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17574.205</t>
+          <t>17574205295.6645</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17388.043</t>
+          <t>17388043047.6838</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17320.845</t>
+          <t>17320845328.4871</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17428.628</t>
+          <t>17428628315.3354</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17228.407</t>
+          <t>17228407474.7265</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17215.902</t>
+          <t>17215902242.6012</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16818.134</t>
+          <t>16818133724.7777</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16724.591</t>
+          <t>16724591080.263</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16988.201</t>
+          <t>16988200784.9589</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16990.102</t>
+          <t>16990101753.6847</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>17020.02</t>
+          <t>17020020048.0185</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>17438.739</t>
+          <t>17438739499.7541</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>17657.584</t>
+          <t>17657583707.0193</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>17022.38</t>
+          <t>17022380302.5826</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21120.992</t>
+          <t>21120992059.2678</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21103.085</t>
+          <t>21103085257.9798</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21257.616</t>
+          <t>21257616267.8664</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21253.457</t>
+          <t>21253457067.6056</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20991.268</t>
+          <t>20991267736.0744</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20786.503</t>
+          <t>20786503218.1709</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20707.222</t>
+          <t>20707221502.5006</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20498.035</t>
+          <t>20498034905.5748</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20322.563</t>
+          <t>20322563303.6011</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>20313.395</t>
+          <t>20313394762.9185</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>20460.883</t>
+          <t>20460883411.1362</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>20452.13</t>
+          <t>20452130215.4491</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>20449.24</t>
+          <t>20449240107.8375</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20177.933</t>
+          <t>20177933177.2751</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>19761.315</t>
+          <t>19761314827.713</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4602.365</t>
+          <t>4602364859.91545</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4544.019</t>
+          <t>4544019428.83755</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4362.778</t>
+          <t>4362777968.03455</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4455.978</t>
+          <t>4455977994.00745</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4556.646</t>
+          <t>4556645705.75623</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4516.293</t>
+          <t>4516293326</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4458.095</t>
+          <t>4458094735</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4368.796</t>
+          <t>4368796377</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4334.676</t>
+          <t>4334676015</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4271.93</t>
+          <t>4271929582</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4255.257</t>
+          <t>4255257495</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4449.885</t>
+          <t>4449884580</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4460.754</t>
+          <t>4460754272</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4325.849</t>
+          <t>4325848530.13545</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4460.831</t>
+          <t>4460831251.99485</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5209.21</t>
+          <t>5209210053.16558</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5199.909</t>
+          <t>5199909471.16768</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5208.018</t>
+          <t>5208017966.02961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5302.426</t>
+          <t>5302426129.14995</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5410.449</t>
+          <t>5410448626.82172</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5414.654</t>
+          <t>5414654180</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5245.7</t>
+          <t>5245699904</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5242.508</t>
+          <t>5242507923</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5082.214</t>
+          <t>5082214091</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5006.095</t>
+          <t>5006094922</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4867.097</t>
+          <t>4867097044</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4875.492</t>
+          <t>4875491546</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4841.612</t>
+          <t>4841611676</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4569.427</t>
+          <t>4569426721.06114</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4521.814</t>
+          <t>4521813965.77873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>86952.893</t>
+          <t>86952892611.5324</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>87438.068</t>
+          <t>87438067861.1118</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84418.096</t>
+          <t>84418096039.5599</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>86837.332</t>
+          <t>86837332428.3994</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>94290.504</t>
+          <t>94290504041.1305</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>101048.738</t>
+          <t>101048738349.897</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>102140.782</t>
+          <t>102140782387.125</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>106924.607</t>
+          <t>106924606918.56</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>109620.078</t>
+          <t>109620077805.19</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>110493.55</t>
+          <t>110493549859.81</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>99923.416</t>
+          <t>99923415699.6597</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>93261.855</t>
+          <t>93261855406.52</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>95786.544</t>
+          <t>95786544168.8166</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>96544.284</t>
+          <t>96544284148.1362</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>98119.481</t>
+          <t>98119480612.5981</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>723076.409</t>
+          <t>723076409333.972</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>747215.332</t>
+          <t>747215332261.336</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>752837.021</t>
+          <t>752837021009.415</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>756929.543</t>
+          <t>756929542690.569</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>746019.624</t>
+          <t>746019624387.059</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>781925.874</t>
+          <t>781925874346.531</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>812716.587</t>
+          <t>812716586782.167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>795096.176</t>
+          <t>795096175791.309</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>837838.165</t>
+          <t>837838165211.409</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>858980.337</t>
+          <t>858980336847.489</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>885756.794</t>
+          <t>885756793544.627</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>891991.724</t>
+          <t>891991724304.385</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>865421.094</t>
+          <t>865421094492.764</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>868817.397</t>
+          <t>868817397453.202</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>870718.141</t>
+          <t>870718140842.123</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1481.971</t>
+          <t>1481970602.21181</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1531.064</t>
+          <t>1531063892.41817</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1583.823</t>
+          <t>1583822946.40331</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1656.031</t>
+          <t>1656030558.37997</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1735.007</t>
+          <t>1735006644.63146</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1797.458</t>
+          <t>1797458421.50389</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1847.257</t>
+          <t>1847256940.33823</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1841.8</t>
+          <t>1841799850.98145</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1859.188</t>
+          <t>1859187886.45714</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1907.23</t>
+          <t>1907230305.88212</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1990.431</t>
+          <t>1990430895.82127</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2088.801</t>
+          <t>2088800836.20737</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2120.638</t>
+          <t>2120637705.83515</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2138.98</t>
+          <t>2138979844.79252</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1944.717</t>
+          <t>1944717074.47156</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20399.66</t>
+          <t>20399659973.0691</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20345.972</t>
+          <t>20345972185.5228</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20369.614</t>
+          <t>20369613545.4545</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20682.862</t>
+          <t>20682862103.7944</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20604.667</t>
+          <t>20604667128.9301</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20395.144</t>
+          <t>20395143817.0313</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20577.864</t>
+          <t>20577864273.4922</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20552.314</t>
+          <t>20552313900.7907</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20506.357</t>
+          <t>20506357017.7394</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>20652.343</t>
+          <t>20652343353.669</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>20631.173</t>
+          <t>20631173222.9741</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20930.295</t>
+          <t>20930294616.9981</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>21202.478</t>
+          <t>21202477611.8916</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>21034.313</t>
+          <t>21034312544.3434</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19932.11</t>
+          <t>19932109820.2697</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>67830.982</t>
+          <t>67830981747.0877</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>67759.544</t>
+          <t>67759544081.4378</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67164.174</t>
+          <t>67164174229.5255</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>64244.267</t>
+          <t>64244267414.4727</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>62572.877</t>
+          <t>62572876558.6753</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>62303.739</t>
+          <t>62303739123.5402</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60928.927</t>
+          <t>60928926715.3596</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>59174.466</t>
+          <t>59174466443.0998</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>59068.304</t>
+          <t>59068304061.9611</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>58726.675</t>
+          <t>58726675094.6917</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>57698.989</t>
+          <t>57698989208.9644</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>58047.348</t>
+          <t>58047348136.3628</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>58143.697</t>
+          <t>58143697492.65</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>56236.612</t>
+          <t>56236611606.1829</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>51823.639</t>
+          <t>51823638888.904</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>28619.112</t>
+          <t>28619111712.7211</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27822.144</t>
+          <t>27822143889.0005</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27387.823</t>
+          <t>27387822634.399</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25177.847</t>
+          <t>25177846595.1586</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>25855.563</t>
+          <t>25855562633.2732</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>26568.963</t>
+          <t>26568962791.8559</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26135.509</t>
+          <t>26135509456.5117</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26195.6</t>
+          <t>26195599527.1957</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26324.079</t>
+          <t>26324079477.8952</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27295.822</t>
+          <t>27295821939.2313</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>26174.3</t>
+          <t>26174299894.4793</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26083.912</t>
+          <t>26083911950.3647</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>25445.415</t>
+          <t>25445415330.4625</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>25600.676</t>
+          <t>25600676227.8962</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>25523.589</t>
+          <t>25523588649.4501</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1744.13</t>
+          <t>1744129738.17035</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1753.35</t>
+          <t>1753350332.98209</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1699.009</t>
+          <t>1699009108.78661</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1785.68</t>
+          <t>1785679915.40786</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1681.36</t>
+          <t>1681359801.51844</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1711.461</t>
+          <t>1711461074.03315</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1628.994</t>
+          <t>1628993904.65116</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1633.804</t>
+          <t>1633804183.06636</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1670.765</t>
+          <t>1670764707.15835</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1649.612</t>
+          <t>1649612274.76038</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1736.928</t>
+          <t>1736928496.27263</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1700.906</t>
+          <t>1700905800.8089</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1753.234</t>
+          <t>1753234285.45781</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1699.062</t>
+          <t>1699062060.21834</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1554.489</t>
+          <t>1554488629.00202</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>158.075</t>
+          <t>158075180.342627</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>161.749</t>
+          <t>161749101.642942</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>166.118</t>
+          <t>166118228.130983</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>169.787</t>
+          <t>169786502.621223</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>169.277</t>
+          <t>169277271.712267</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>178.689</t>
+          <t>178689065.83065</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>184.611</t>
+          <t>184611076.568658</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>191.351</t>
+          <t>191350976.870756</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>205.864</t>
+          <t>205864271.40472</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>210.989</t>
+          <t>210988658.321555</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>215.995</t>
+          <t>215995337.535135</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>221.506</t>
+          <t>221505577.28766</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>228.382</t>
+          <t>228381980.196782</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>245.812</t>
+          <t>245812406.87221</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>247.307</t>
+          <t>247306639.415579</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>946.518</t>
+          <t>946518394.206409</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>927.107</t>
+          <t>927107103.670811</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>957.355</t>
+          <t>957355015.542396</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>934.932</t>
+          <t>934931976.631715</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>878.324</t>
+          <t>878324100.216735</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>795.865</t>
+          <t>795865352.560998</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>778.262</t>
+          <t>778262096.331601</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>760.647</t>
+          <t>760647326.174309</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>779.506</t>
+          <t>779505761.85751</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>777.81</t>
+          <t>777810378.292613</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>792.997</t>
+          <t>792997025.002153</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>821.843</t>
+          <t>821842613.635836</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>838.459</t>
+          <t>838459293.202901</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>802.475</t>
+          <t>802475049.251403</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>588.259</t>
+          <t>588258578.866705</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>43256.391</t>
+          <t>43256391348.6269</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>45122.322</t>
+          <t>45122322427.8983</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>45753.032</t>
+          <t>45753031812.4012</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>47101.808</t>
+          <t>47101808286.4484</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48491.699</t>
+          <t>48491698990.1776</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>49572.582</t>
+          <t>49572581608.1555</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>49769.366</t>
+          <t>49769366333.8815</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>49963.281</t>
+          <t>49963280655.3518</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>51549.982</t>
+          <t>51549981516.1089</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>53744.845</t>
+          <t>53744845463.3453</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>53619.006</t>
+          <t>53619005679.0345</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>54363.492</t>
+          <t>54363492072.6707</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>54502.262</t>
+          <t>54502262313.9136</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>58923.82</t>
+          <t>58923820417.6452</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>57751.234</t>
+          <t>57751233848.2803</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>131.528</t>
+          <t>131527773.490009</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>132.109</t>
+          <t>132109117.02421</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>132.636</t>
+          <t>132635689.349404</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>134.476</t>
+          <t>134476290.241573</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>136.295</t>
+          <t>136295270.91966</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>137.834</t>
+          <t>137833669.263885</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>118.833</t>
+          <t>118833303.022133</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>140.257</t>
+          <t>140257011.824327</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>129.738</t>
+          <t>129737837.27676</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>130.205</t>
+          <t>130204934.758125</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>127.448</t>
+          <t>127447813.064936</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>128.563</t>
+          <t>128563139.080731</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>128.346</t>
+          <t>128345935.249053</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>122.178</t>
+          <t>122177986.855328</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>120.087</t>
+          <t>120087381.584778</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4826.064</t>
+          <t>4826064126.32517</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4878.45</t>
+          <t>4878450374.07404</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4988.051</t>
+          <t>4988050800.97069</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4997.4</t>
+          <t>4997399926.4115</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5099.317</t>
+          <t>5099317266.45304</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5215.279</t>
+          <t>5215278555.96398</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5277.074</t>
+          <t>5277073886</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5296.494</t>
+          <t>5296493607</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5268.557</t>
+          <t>5268557297</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5195.236</t>
+          <t>5195236243</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>5162.653</t>
+          <t>5162652590</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5193.072</t>
+          <t>5193072191</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>5249.601</t>
+          <t>5249601208</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>5366.081</t>
+          <t>5366080802.23595</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5327.881</t>
+          <t>5327881394.84444</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20654.901</t>
+          <t>20654900843.8376</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20980.832</t>
+          <t>20980831974.6441</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21113.723</t>
+          <t>21113723481.3001</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20980.798</t>
+          <t>20980797813.9312</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20211.527</t>
+          <t>20211527086.5954</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>19838.962</t>
+          <t>19838962021.7287</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17312.98</t>
+          <t>17312979533.4311</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16465.691</t>
+          <t>16465691448.7976</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16161.418</t>
+          <t>16161417806.6431</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>16214.738</t>
+          <t>16214737533.9096</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16416.202</t>
+          <t>16416202129.8764</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>16720.432</t>
+          <t>16720431594.8281</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>17088.461</t>
+          <t>17088460523.312</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>17751.83</t>
+          <t>17751830418.9761</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>17123.852</t>
+          <t>17123852085.6202</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5079.376</t>
+          <t>5079375755.78437</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5099.4</t>
+          <t>5099400301.39985</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5106.684</t>
+          <t>5106684179.49939</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5141.818</t>
+          <t>5141817656.24214</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5199.044</t>
+          <t>5199044081.35927</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5330.282</t>
+          <t>5330281665.94049</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5317.792</t>
+          <t>5317792481.37372</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5313.819</t>
+          <t>5313818822.53819</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5161.252</t>
+          <t>5161251820.43981</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5111.023</t>
+          <t>5111022850.47712</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5005.324</t>
+          <t>5005323760.63136</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5028.754</t>
+          <t>5028753663.36687</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5006.548</t>
+          <t>5006548433.76241</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>4930.457</t>
+          <t>4930457438.09974</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4761.6</t>
+          <t>4761600251.85481</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>14019.638</t>
+          <t>14019637533.9338</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>14325.604</t>
+          <t>14325603571.388</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13571.066</t>
+          <t>13571066383.7692</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13100.784</t>
+          <t>13100784250.9917</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16057.962</t>
+          <t>16057962000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15831.996</t>
+          <t>15831996000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15625.169</t>
+          <t>15625169000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>13670.158</t>
+          <t>13670158000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13444.372</t>
+          <t>13444372000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>12688.209</t>
+          <t>12688209000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>12527.219</t>
+          <t>12527219000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>12532.295</t>
+          <t>12532295000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>12570.825</t>
+          <t>12570825000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>12577.394</t>
+          <t>12577394000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>12220.634</t>
+          <t>12220634452.4776</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>110870.466</t>
+          <t>110870466145.887</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>107769.48</t>
+          <t>107769480245.457</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>102879.858</t>
+          <t>102879858248.431</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>97604.423</t>
+          <t>97604422654.543</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>97660.713</t>
+          <t>97660712820.1894</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>98438.411</t>
+          <t>98438410980.0906</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>98012.043</t>
+          <t>98012043179.9487</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>97278.059</t>
+          <t>97278058938.7505</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>96797.263</t>
+          <t>96797263325.6221</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>96540.914</t>
+          <t>96540913578.2419</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>95904.557</t>
+          <t>95904556540.5806</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>95992.613</t>
+          <t>95992613449.7149</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>96504.218</t>
+          <t>96504218395.0272</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>96160.797</t>
+          <t>96160797350.6376</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>92874.538</t>
+          <t>92874537696.9292</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2592.421</t>
+          <t>2592421000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2532.052</t>
+          <t>2532052000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2485.971</t>
+          <t>2485971000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2399.056</t>
+          <t>2399056000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2285.215</t>
+          <t>2285215000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2212.396</t>
+          <t>2212396000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2172.08</t>
+          <t>2172080000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2064.652</t>
+          <t>2064652000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2012.49</t>
+          <t>2012490000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2061.732</t>
+          <t>2061732000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2053.76</t>
+          <t>2053760000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2025.27</t>
+          <t>2025270000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2096.466</t>
+          <t>2096466000</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2195.148</t>
+          <t>2195147867.2278</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2102.708</t>
+          <t>2102707646.83797</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1172.176</t>
+          <t>1172176200.32428</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1124.012</t>
+          <t>1124011787.04834</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1100.209</t>
+          <t>1100208812.70175</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1083.98</t>
+          <t>1083980262.16165</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1079.684</t>
+          <t>1079684269.00381</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1077.527</t>
+          <t>1077526852.08965</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1071.911</t>
+          <t>1071910634.01072</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1057.675</t>
+          <t>1057674768.49686</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1041.358</t>
+          <t>1041357624.38832</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1032.195</t>
+          <t>1032194981.12369</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1027.936</t>
+          <t>1027936016.9503</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1028.699</t>
+          <t>1028699102.39496</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1048.541</t>
+          <t>1048541086.05704</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1101.374</t>
+          <t>1101373985.19625</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1042.683</t>
+          <t>1042682541.32371</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3921.84</t>
+          <t>3921840000</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3903.08</t>
+          <t>3903080000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3844.12</t>
+          <t>3844120000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3894.96</t>
+          <t>3894960000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3973.45</t>
+          <t>3973450000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4002.83</t>
+          <t>4002830000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4037.99</t>
+          <t>4037990000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3999.39</t>
+          <t>3999390000</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>3935.33</t>
+          <t>3935330000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3950.53</t>
+          <t>3950530000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3935.78</t>
+          <t>3935780000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>3934.96</t>
+          <t>3934960000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4063.59</t>
+          <t>4063590000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4112.632</t>
+          <t>4112632066.22711</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3987.768</t>
+          <t>3987768359.95138</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>32012.647</t>
+          <t>32012647238.2097</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>33301.74</t>
+          <t>33301739884.3458</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>33223.586</t>
+          <t>33223586053.8934</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31936.066</t>
+          <t>31936065666.6704</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>31633.693</t>
+          <t>31633692642.3538</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>29183.918</t>
+          <t>29183917684.3217</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>29160.201</t>
+          <t>29160201410.5935</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28028.148</t>
+          <t>28028148204.4303</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27266.141</t>
+          <t>27266141383.5484</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27761.458</t>
+          <t>27761458063.3163</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>27475.823</t>
+          <t>27475822998.6693</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26155.51</t>
+          <t>26155510292.0869</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>24472.766</t>
+          <t>24472765612.4533</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>24922.145</t>
+          <t>24922145213.6911</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>24478.283</t>
+          <t>24478283414.706</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12599.261</t>
+          <t>12599260952.7067</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12302.965</t>
+          <t>12302964897.5388</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12502.164</t>
+          <t>12502164134.5941</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12292.227</t>
+          <t>12292227223.5654</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12152.357</t>
+          <t>12152356917.4732</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12225.902</t>
+          <t>12225901856.4505</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11267.711</t>
+          <t>11267710551.2568</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11234.983</t>
+          <t>11234982776.9988</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>11319.506</t>
+          <t>11319506024.7481</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>11586.799</t>
+          <t>11586798987.223</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>11752.07</t>
+          <t>11752069509.8024</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>11846.395</t>
+          <t>11846394746.0835</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12094.065</t>
+          <t>12094064596.8221</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12136.763</t>
+          <t>12136763200.818</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>11385.779</t>
+          <t>11385779446.3724</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>93651.416</t>
+          <t>93651415551.8366</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>94805.194</t>
+          <t>94805193725.4861</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>97020.9</t>
+          <t>97020900130.2675</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>98733.989</t>
+          <t>98733988915.7743</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>99810.664</t>
+          <t>99810663841.7137</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>102085.127</t>
+          <t>102085127147.043</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100171.555</t>
+          <t>100171554541.105</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>97904.897</t>
+          <t>97904896782.3505</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>96923.77</t>
+          <t>96923770425.9432</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>98190.3</t>
+          <t>98190300172.9559</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>99088.455</t>
+          <t>99088454732.8965</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>101618.572</t>
+          <t>101618572365.201</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>101523.525</t>
+          <t>101523524686.793</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>99562.196</t>
+          <t>99562195536.8395</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>93448.649</t>
+          <t>93448649096.0491</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1349194.712</t>
+          <t>1349194711912.82</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1376986.267</t>
+          <t>1376986266558.49</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1399861.801</t>
+          <t>1399861801088.96</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1419511.753</t>
+          <t>1419511753335.98</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1442587.813</t>
+          <t>1442587813367.67</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1500149.112</t>
+          <t>1500149111844.83</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1549300.1</t>
+          <t>1549300099794.48</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1599158.289</t>
+          <t>1599158289186</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1666535.691</t>
+          <t>1666535691327.72</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1714831.804</t>
+          <t>1714831804475.5</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1751342.171</t>
+          <t>1751342171202.12</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1817422.899</t>
+          <t>1817422899264.31</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1834927.741</t>
+          <t>1834927740539.67</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1890700.18</t>
+          <t>1890700180462.9</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1914603.455</t>
+          <t>1914603455316.38</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3770600.774</t>
+          <t>3770600774381.09</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3823027.618</t>
+          <t>3823027618459.62</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3849596.965</t>
+          <t>3849596965019.25</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3862635.749</t>
+          <t>3862635748791.21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3896530.293</t>
+          <t>3896530293164.64</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4009398.674</t>
+          <t>4009398673836.07</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4099331.63</t>
+          <t>4099331630233.11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4151918.433</t>
+          <t>4151918432744.4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4281294.224</t>
+          <t>4281294223835.63</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4374853.171</t>
+          <t>4374853171051.62</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>4430629.409</t>
+          <t>4430629409204.04</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4531523.676</t>
+          <t>4531523676337.63</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>4549912.179</t>
+          <t>4549912179314.16</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>4644530.653</t>
+          <t>4644530652785.26</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>4649345.326</t>
+          <t>4649345325734.26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
